--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
@@ -362,7 +362,7 @@
     <t>FON-63</t>
   </si>
   <si>
-    <t>Coordonnateur en EPHAD</t>
+    <t>Coordonnateur en EHPAD</t>
   </si>
   <si>
     <t>FON-AU</t>
